--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487079_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487079_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2124</v>
+        <v>8.826499999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7939</v>
+        <v>7.0333</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4185</v>
+        <v>1.7933</v>
       </c>
       <c r="G2" t="n">
         <v>5.9698</v>
@@ -610,13 +610,13 @@
         <v>2.8951</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.8383</v>
+        <v>-1.2242</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1012</v>
+        <v>0.1382</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.7371</v>
+        <v>-1.3623</v>
       </c>
       <c r="V2" t="n">
         <v>1.1857</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.664</v>
+        <v>5.4909</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4183</v>
+        <v>4.8972</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2458</v>
+        <v>0.5938</v>
       </c>
       <c r="G3" t="n">
         <v>5.1822</v>
@@ -688,13 +688,13 @@
         <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4905</v>
+        <v>-0.6636</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2697</v>
+        <v>0.2092</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2209</v>
+        <v>-0.8729</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5717</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>J. DOSS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3286</v>
+        <v>1.5587</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.7786</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4682</v>
+        <v>0.7801</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5119</v>
+        <v>3.016</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6062</v>
+        <v>1.8279</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09429999999999999</v>
+        <v>1.1881</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7855</v>
+        <v>3.0628</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7952</v>
+        <v>2.3959</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.0096</v>
+        <v>0.6669</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2736</v>
+        <v>-0.0468</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.189</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9154</v>
+        <v>0.5212</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.386</v>
+        <v>0.386</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5091</v>
+        <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3028</v>
+        <v>-0.9013</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8421</v>
+        <v>0.0162</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4606</v>
+        <v>-0.9175</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8999</v>
+        <v>-0.9421</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1278</v>
+        <v>-0.3704</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.228</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8203</v>
+        <v>1.5467</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1634</v>
+        <v>0.863</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6569</v>
+        <v>0.6837</v>
       </c>
       <c r="G5" t="n">
         <v>0.9419</v>
@@ -844,13 +844,13 @@
         <v>0.579</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2994</v>
+        <v>0.0258</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5486</v>
+        <v>0.2482</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2492</v>
+        <v>-0.2224</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3672</v>
+        <v>1.4803</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6435</v>
+        <v>1.944</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2763</v>
+        <v>-0.4637</v>
       </c>
       <c r="G6" t="n">
         <v>3.0208</v>
@@ -922,13 +922,13 @@
         <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5837</v>
+        <v>-0.4706</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4759</v>
+        <v>-0.1755</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1078</v>
+        <v>-0.2952</v>
       </c>
       <c r="V6" t="n">
         <v>-1.842</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. DOSS</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7387</v>
+        <v>0.8751</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0414</v>
+        <v>0.3974</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7801</v>
+        <v>0.4777</v>
       </c>
       <c r="G7" t="n">
-        <v>3.016</v>
+        <v>0.5119</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8279</v>
+        <v>0.6062</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1881</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>3.0628</v>
+        <v>0.7855</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3959</v>
+        <v>1.7952</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6669</v>
+        <v>-1.0096</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0468</v>
+        <v>-0.2736</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-1.189</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5212</v>
+        <v>0.9154</v>
       </c>
       <c r="P7" t="n">
-        <v>0.386</v>
+        <v>-0.386</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3161</v>
+        <v>2.5091</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7212</v>
+        <v>-0.1507</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8037</v>
+        <v>0.3791</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9175</v>
+        <v>-0.5298</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9421</v>
+        <v>0.8999</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3704</v>
+        <v>2.1278</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5717</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. DINIS</t>
+          <t>S. LOPEZ RAMOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3107</v>
+        <v>0.1781</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9775</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6667999999999999</v>
+        <v>0.1781</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4175</v>
+        <v>0.1335</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.1335</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.397</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7347</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.1317</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8145</v>
+        <v>0.1335</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0198</v>
+        <v>0.1335</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7947</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.772</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7371</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0054</v>
+        <v>0.0446</v>
       </c>
       <c r="T8" t="n">
-        <v>1.482</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4766</v>
+        <v>0.0446</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8842</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8576</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. LOPEZ RAMOS</t>
+          <t>A. DINIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1514</v>
+        <v>-0.0304</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.3955</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1514</v>
+        <v>-0.4259</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1335</v>
+        <v>0.4175</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1335</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.397</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.7347</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.1317</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1335</v>
+        <v>0.8145</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1335</v>
+        <v>0.0198</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.7947</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.772</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.7371</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0178</v>
+        <v>0.6643</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0178</v>
+        <v>-0.2357</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.8842</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8576</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.326</v>
+        <v>-1.2679</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6653</v>
+        <v>-2.6072</v>
       </c>
       <c r="F10" t="n">
         <v>1.3393</v>
@@ -1234,10 +1234,10 @@
         <v>2.1231</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7853</v>
+        <v>-0.1566</v>
       </c>
       <c r="T10" t="n">
-        <v>1.363</v>
+        <v>0.4211</v>
       </c>
       <c r="U10" t="n">
         <v>-0.5777</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3014</v>
+        <v>-1.5012</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6665</v>
+        <v>-1.9466</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3651</v>
+        <v>0.4454</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3247</v>
@@ -1312,13 +1312,13 @@
         <v>0.965</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1191</v>
+        <v>-0.3189</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5354</v>
+        <v>0.1844</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5837</v>
+        <v>-0.5034</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8576</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4258</v>
+        <v>-5.4268</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2332</v>
+        <v>-2.3145</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1926</v>
+        <v>-3.1123</v>
       </c>
       <c r="G12" t="n">
         <v>-0.198</v>
@@ -1390,13 +1390,13 @@
         <v>0.965</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.5569</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2657</v>
+        <v>0.1844</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8216</v>
+        <v>-0.7413</v>
       </c>
       <c r="V12" t="n">
         <v>-2.7418</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.5401</v>
+        <v>11.73</v>
       </c>
       <c r="E13" t="n">
-        <v>8.250599999999999</v>
+        <v>9.440699999999996</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2896</v>
+        <v>2.2895</v>
       </c>
       <c r="G13" t="n">
         <v>18.6176</v>
@@ -1453,7 +1453,7 @@
         <v>2.9378</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.3094</v>
+        <v>-4.309400000000001</v>
       </c>
       <c r="O13" t="n">
         <v>7.2472</v>
@@ -1468,13 +1468,13 @@
         <v>16.4056</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.898</v>
+        <v>-3.7081</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3155</v>
+        <v>2.505300000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.213700000000001</v>
+        <v>-6.2136</v>
       </c>
       <c r="V13" t="n">
         <v>-7.0397</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0535</v>
+        <v>6.0168</v>
       </c>
       <c r="E14" t="n">
-        <v>6.3259</v>
+        <v>5.8252</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7276</v>
+        <v>0.1916</v>
       </c>
       <c r="G14" t="n">
         <v>0.5937</v>
@@ -1546,13 +1546,13 @@
         <v>1.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4755</v>
+        <v>2.4387</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0002</v>
+        <v>1.4995</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4753</v>
+        <v>0.9392</v>
       </c>
       <c r="V14" t="n">
         <v>2.2123</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1107</v>
+        <v>3.7898</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6994</v>
+        <v>4.2989</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5887</v>
+        <v>-0.5091</v>
       </c>
       <c r="G15" t="n">
         <v>1.0212</v>
@@ -1624,13 +1624,13 @@
         <v>1.3511</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3247</v>
+        <v>2.0038</v>
       </c>
       <c r="T15" t="n">
-        <v>1.749</v>
+        <v>1.3484</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5757</v>
+        <v>0.6553</v>
       </c>
       <c r="V15" t="n">
         <v>0.5717</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. OLIVEIRA GETE</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6263</v>
+        <v>1.0442</v>
       </c>
       <c r="E16" t="n">
-        <v>1.85</v>
+        <v>1.6377</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2237</v>
+        <v>-0.5935</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5327</v>
+        <v>-1.2626</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4388</v>
+        <v>0.3375</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0939</v>
+        <v>-1.6001</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2381</v>
+        <v>0.5322</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4295</v>
+        <v>1.1592</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6676</v>
+        <v>-0.6269</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2945</v>
+        <v>-1.7948</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8682</v>
+        <v>-0.8216</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4263</v>
+        <v>-0.9732</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3511</v>
+        <v>-1.158</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3511</v>
+        <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3207</v>
+        <v>0.0668</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6009</v>
+        <v>0.3166</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2803</v>
+        <v>-0.2499</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4873</v>
+        <v>3.398</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4873</v>
+        <v>3.6839</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. SAGASTI ARGOTE</t>
+          <t>A. OLIVEIRA GETE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5199</v>
+        <v>0.8252</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4387</v>
+        <v>1.0489</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.2237</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3436</v>
+        <v>-1.5327</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.948</v>
+        <v>-0.4388</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3956</v>
+        <v>-1.0939</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9488</v>
+        <v>-0.2381</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9731</v>
+        <v>0.4295</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0243</v>
+        <v>-0.6676</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3948</v>
+        <v>-1.2945</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9749</v>
+        <v>-0.8682</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4199</v>
+        <v>-0.4263</v>
       </c>
       <c r="P17" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4774</v>
+        <v>0.5195</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3875</v>
+        <v>0.7998</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08989999999999999</v>
+        <v>-0.2803</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.4873</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.4873</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1978</v>
+        <v>-0.3631</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6363</v>
+        <v>-0.4228</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8341</v>
+        <v>0.0598</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2626</v>
+        <v>-0.8861</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3375</v>
+        <v>-2.5419</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6001</v>
+        <v>1.6558</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5322</v>
+        <v>-0.2651</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1592</v>
+        <v>-0.8591</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6269</v>
+        <v>0.5941</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7948</v>
+        <v>-0.621</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8216</v>
+        <v>-1.6828</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9732</v>
+        <v>1.0617</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.158</v>
+        <v>-0.772</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7371</v>
+        <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1752</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6848</v>
+        <v>0.2585</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4905</v>
+        <v>-0.1914</v>
       </c>
       <c r="V18" t="n">
-        <v>3.398</v>
+        <v>1.228</v>
       </c>
       <c r="W18" t="n">
-        <v>3.6839</v>
+        <v>1.5138</v>
       </c>
       <c r="X18" t="n">
         <v>-0.2859</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>I. SAGASTI ARGOTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1777</v>
+        <v>-0.7486</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0237</v>
+        <v>0.0368</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1541</v>
+        <v>-0.7853</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8861</v>
+        <v>-2.3436</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.5419</v>
+        <v>-1.948</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6558</v>
+        <v>-0.3956</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2651</v>
+        <v>-0.9488</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8591</v>
+        <v>-0.9731</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5941</v>
+        <v>0.0243</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.621</v>
+        <v>-1.3948</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6828</v>
+        <v>-0.9749</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0617</v>
+        <v>-0.4199</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.772</v>
+        <v>0.386</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7476</v>
+        <v>1.209</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3424</v>
+        <v>0.9856</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4052</v>
+        <v>0.2234</v>
       </c>
       <c r="V19" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6486</v>
+        <v>-2.6615</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4838</v>
+        <v>-2.684</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1648</v>
+        <v>0.0225</v>
       </c>
       <c r="G20" t="n">
         <v>0.6526999999999999</v>
@@ -2014,13 +2014,13 @@
         <v>0.965</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.499</v>
+        <v>-0.5119</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3107</v>
+        <v>0.1104</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8097</v>
+        <v>-0.6223</v>
       </c>
       <c r="V20" t="n">
         <v>0.2859</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1052</v>
+        <v>-3.9188</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8915</v>
+        <v>-3.4909</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2137</v>
+        <v>-0.4279</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4833</v>
@@ -2092,13 +2092,13 @@
         <v>0.579</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.587</v>
+        <v>-0.4006</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5949</v>
+        <v>-0.1943</v>
       </c>
       <c r="U21" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.2062</v>
       </c>
       <c r="V21" t="n">
         <v>-0.614</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.299</v>
+        <v>-5.3168</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4847</v>
+        <v>-2.984</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8143</v>
+        <v>-2.3328</v>
       </c>
       <c r="G22" t="n">
         <v>-3.7259</v>
@@ -2170,13 +2170,13 @@
         <v>1.5441</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8084</v>
+        <v>0.1738</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0423</v>
+        <v>0.543</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8507</v>
+        <v>-0.3692</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1857</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.4223</v>
+        <v>-7.8722</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.0704</v>
+        <v>-5.2692</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3519</v>
+        <v>-2.603</v>
       </c>
       <c r="G23" t="n">
         <v>-7.6514</v>
@@ -2248,13 +2248,13 @@
         <v>1.5441</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8831</v>
+        <v>0.6669</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2551</v>
+        <v>0.546</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.628</v>
+        <v>0.1209</v>
       </c>
       <c r="V23" t="n">
         <v>0.6562</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.5402</v>
+        <v>-9.205</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.003800000000001</v>
+        <v>-2.003400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.5366</v>
+        <v>-7.2014</v>
       </c>
       <c r="G24" t="n">
         <v>-18.618</v>
@@ -2299,7 +2299,7 @@
         <v>-14.9124</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.937899999999999</v>
+        <v>-2.9379</v>
       </c>
       <c r="K24" t="n">
         <v>4.3095</v>
@@ -2326,16 +2326,16 @@
         <v>12.5456</v>
       </c>
       <c r="S24" t="n">
-        <v>4.898000000000001</v>
+        <v>6.233099999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>6.213400000000001</v>
+        <v>6.213500000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.315599999999999</v>
+        <v>0.01950000000000006</v>
       </c>
       <c r="V24" t="n">
-        <v>7.039700000000001</v>
+        <v>7.0397</v>
       </c>
       <c r="W24" t="n">
         <v>11.1263</v>
